--- a/TalkTukTuk_Phrases.xlsx
+++ b/TalkTukTuk_Phrases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TOSHIBA\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8BDF50-4C54-4194-9DE8-6316D0798F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4327ECA5-66AC-4F91-B102-EFC981836DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="765" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phrases" sheetId="1" r:id="rId1"/>

--- a/TalkTukTuk_Phrases.xlsx
+++ b/TalkTukTuk_Phrases.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TOSHIBA\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD88810-1231-4A12-A487-F436FDA2E319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935F2BCC-B0A7-45D4-BD0A-D91045E83AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phrases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="298">
   <si>
     <t>PhraseID</t>
   </si>
@@ -628,9 +628,6 @@
     <t>ថ្ងៃចន្ទ</t>
   </si>
   <si>
-    <t>Tngai Chan</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-DAY-001.mp4</t>
   </si>
   <si>
@@ -649,9 +646,6 @@
     <t>ថ្ងៃអង្គារ</t>
   </si>
   <si>
-    <t>Tngai Angkear</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-DAY-002.mp4</t>
   </si>
   <si>
@@ -664,9 +658,6 @@
     <t>ថ្ងៃពុធ</t>
   </si>
   <si>
-    <t>Tngai Put</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-DAY-003.mp4</t>
   </si>
   <si>
@@ -679,9 +670,6 @@
     <t>ថ្ងៃព្រហស្បតិ៍</t>
   </si>
   <si>
-    <t>Tngai Prohoas</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-DAY-004.mp4</t>
   </si>
   <si>
@@ -694,9 +682,6 @@
     <t>ថ្ងៃសុក្រ</t>
   </si>
   <si>
-    <t>Tngai Sok</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-DAY-005.mp4</t>
   </si>
   <si>
@@ -709,9 +694,6 @@
     <t>ថ្ងៃសៅរ៍</t>
   </si>
   <si>
-    <t>Tngai Sau</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-DAY-006.mp4</t>
   </si>
   <si>
@@ -724,9 +706,6 @@
     <t>ថ្ងៃអាទិត្យ</t>
   </si>
   <si>
-    <t>Tngai Artit</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-DAY-007.mp4</t>
   </si>
   <si>
@@ -739,9 +718,6 @@
     <t>ចុងសប្តាហ៍</t>
   </si>
   <si>
-    <t>Chong Sabda</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-DAY-008.mp4</t>
   </si>
   <si>
@@ -899,6 +875,45 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-DAY-009.mp4</t>
+  </si>
+  <si>
+    <t>Kani Chan</t>
+  </si>
+  <si>
+    <t>Kani  Angkear</t>
+  </si>
+  <si>
+    <t>Kani  Put</t>
+  </si>
+  <si>
+    <t>Kani  Prohoas</t>
+  </si>
+  <si>
+    <t>Kani Sok</t>
+  </si>
+  <si>
+    <t>Kani  Sau</t>
+  </si>
+  <si>
+    <t>Kani Artit</t>
+  </si>
+  <si>
+    <t>Kani Chong Sabda</t>
+  </si>
+  <si>
+    <t>PHR-SOC-007</t>
+  </si>
+  <si>
+    <t>Please</t>
+  </si>
+  <si>
+    <t>សូម</t>
+  </si>
+  <si>
+    <t>Som</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-007.mp4</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2066,19 +2081,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>125</v>
@@ -2091,46 +2106,46 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H29" s="10" t="s">
+      <c r="A29" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>152</v>
@@ -2144,19 +2159,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>152</v>
@@ -2170,19 +2185,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>152</v>
@@ -2196,19 +2211,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>152</v>
@@ -2222,19 +2237,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>152</v>
@@ -2248,19 +2263,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>152</v>
@@ -2274,19 +2289,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>152</v>
@@ -2300,19 +2315,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>152</v>
@@ -2326,19 +2341,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>152</v>
@@ -2351,52 +2366,52 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="H39" s="12" t="s">
+      <c r="A39" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>209</v>
+        <v>285</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="F40" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G40" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>205</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>15</v>
@@ -2404,25 +2419,25 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>214</v>
+        <v>286</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="F41" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G41" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>205</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>15</v>
@@ -2430,25 +2445,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>219</v>
+        <v>287</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="F42" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G42" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>205</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>15</v>
@@ -2456,25 +2471,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="F43" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G43" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>205</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>15</v>
@@ -2482,25 +2497,25 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>229</v>
+        <v>289</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="F44" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G44" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>205</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>15</v>
@@ -2508,25 +2523,25 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>234</v>
+        <v>290</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="F45" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G45" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>205</v>
       </c>
       <c r="H45" s="12" t="s">
         <v>15</v>
@@ -2534,25 +2549,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="E46" s="17" t="s">
-        <v>240</v>
+        <v>291</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>228</v>
       </c>
       <c r="F46" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G46" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>205</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>15</v>
@@ -2560,73 +2575,73 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>288</v>
+        <v>229</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>289</v>
+        <v>230</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>290</v>
+        <v>231</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="F47" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G47" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
+      <c r="H47" s="12" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>15</v>
-      </c>
+      <c r="A48" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H49" s="14" t="s">
         <v>15</v>
@@ -2634,25 +2649,25 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H50" s="14" t="s">
         <v>15</v>
@@ -2660,25 +2675,25 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H51" s="14" t="s">
         <v>15</v>
@@ -2686,25 +2701,25 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H52" s="14" t="s">
         <v>15</v>
@@ -2712,25 +2727,25 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H53" s="14" t="s">
         <v>15</v>
@@ -2738,25 +2753,25 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H54" s="14" t="s">
         <v>15</v>
@@ -2764,35 +2779,68 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H55" s="14" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <f ca="1">B2:B57</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E28" r:id="rId1" xr:uid="{9D7F697B-04A3-43D8-834D-1DD935D30A27}"/>
-    <hyperlink ref="E46" r:id="rId2" xr:uid="{AD381954-74B6-4661-84EC-9487E2F47034}"/>
-    <hyperlink ref="E47" r:id="rId3" xr:uid="{7F578AA3-EA40-4432-9E0B-F9D624BADC2E}"/>
+    <hyperlink ref="E47" r:id="rId2" xr:uid="{AD381954-74B6-4661-84EC-9487E2F47034}"/>
+    <hyperlink ref="E48" r:id="rId3" xr:uid="{7F578AA3-EA40-4432-9E0B-F9D624BADC2E}"/>
+    <hyperlink ref="E29" r:id="rId4" xr:uid="{DAF45DFB-C92C-447D-B376-A4C3C7A10344}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TalkTukTuk_Phrases.xlsx
+++ b/TalkTukTuk_Phrases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TOSHIBA\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935F2BCC-B0A7-45D4-BD0A-D91045E83AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0AEC62-431F-409C-A10A-07AFDD78C7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TalkTukTuk_Phrases.xlsx
+++ b/TalkTukTuk_Phrases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TOSHIBA\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0AEC62-431F-409C-A10A-07AFDD78C7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D7E0F3-51F7-4913-ABDE-CA80A1656807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="353">
   <si>
     <t>PhraseID</t>
   </si>
@@ -451,9 +451,6 @@
     <t>PHR-SOC-005</t>
   </si>
   <si>
-    <t>I'm fine</t>
-  </si>
-  <si>
     <t>ខ្ញុំសុខសប្បាយ</t>
   </si>
   <si>
@@ -466,9 +463,6 @@
     <t>PHR-NUM-001</t>
   </si>
   <si>
-    <t>One — ១</t>
-  </si>
-  <si>
     <t>មួយ</t>
   </si>
   <si>
@@ -487,9 +481,6 @@
     <t>PHR-NUM-002</t>
   </si>
   <si>
-    <t>Two — ២</t>
-  </si>
-  <si>
     <t>ពីរ</t>
   </si>
   <si>
@@ -502,9 +493,6 @@
     <t>PHR-NUM-003</t>
   </si>
   <si>
-    <t>Three — ៣</t>
-  </si>
-  <si>
     <t>បី</t>
   </si>
   <si>
@@ -517,9 +505,6 @@
     <t>PHR-NUM-004</t>
   </si>
   <si>
-    <t>Four — ៤</t>
-  </si>
-  <si>
     <t>បួន</t>
   </si>
   <si>
@@ -532,9 +517,6 @@
     <t>PHR-NUM-005</t>
   </si>
   <si>
-    <t>Five — ៥</t>
-  </si>
-  <si>
     <t>ប្រាំ</t>
   </si>
   <si>
@@ -547,9 +529,6 @@
     <t>PHR-NUM-006</t>
   </si>
   <si>
-    <t>Six — ៦</t>
-  </si>
-  <si>
     <t>ប្រាំមួយ</t>
   </si>
   <si>
@@ -562,9 +541,6 @@
     <t>PHR-NUM-007</t>
   </si>
   <si>
-    <t>Seven — ៧</t>
-  </si>
-  <si>
     <t>ប្រាំពីរ</t>
   </si>
   <si>
@@ -577,9 +553,6 @@
     <t>PHR-NUM-008</t>
   </si>
   <si>
-    <t>Eight — ៨</t>
-  </si>
-  <si>
     <t>ប្រាំបី</t>
   </si>
   <si>
@@ -592,9 +565,6 @@
     <t>PHR-NUM-009</t>
   </si>
   <si>
-    <t>Nine — ៩</t>
-  </si>
-  <si>
     <t>ប្រាំបួន</t>
   </si>
   <si>
@@ -607,9 +577,6 @@
     <t>PHR-NUM-010</t>
   </si>
   <si>
-    <t>Ten — ១០</t>
-  </si>
-  <si>
     <t>ដប់</t>
   </si>
   <si>
@@ -914,6 +881,205 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-007.mp4</t>
+  </si>
+  <si>
+    <t>I am fine</t>
+  </si>
+  <si>
+    <t>PHR-SOC-008</t>
+  </si>
+  <si>
+    <t>I am from</t>
+  </si>
+  <si>
+    <t>ខ្ញុំមកពី…</t>
+  </si>
+  <si>
+    <t>Khnhom mok pi…</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-008.mp4</t>
+  </si>
+  <si>
+    <t>PHR-SOC-009</t>
+  </si>
+  <si>
+    <t>Its Ok</t>
+  </si>
+  <si>
+    <t>Min ey te</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-009.mp4</t>
+  </si>
+  <si>
+    <t>PHR-SOC-010</t>
+  </si>
+  <si>
+    <t>I don’t Know</t>
+  </si>
+  <si>
+    <t>ខ្ញុំមិនដឹងទេ</t>
+  </si>
+  <si>
+    <t>Khnhom min deng te</t>
+  </si>
+  <si>
+    <t>មិនអីទេ</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-010.mp4</t>
+  </si>
+  <si>
+    <t>PHR-FOO-010</t>
+  </si>
+  <si>
+    <t>Ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ទឹកកក
+</t>
+  </si>
+  <si>
+    <t>Teuk kôk</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-FOO-010.mp4</t>
+  </si>
+  <si>
+    <t>PHR-FOO-011</t>
+  </si>
+  <si>
+    <t>Cheers</t>
+  </si>
+  <si>
+    <t>ជល់មួយ!</t>
+  </si>
+  <si>
+    <t>Jul muoy!</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-FOO-011.mp4</t>
+  </si>
+  <si>
+    <t>PHR-SOC-011</t>
+  </si>
+  <si>
+    <t>How old are you?</t>
+  </si>
+  <si>
+    <t>អ្នកអាយុប៉ុន្មាន?</t>
+  </si>
+  <si>
+    <t>Nak ayu ponman?</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-011.mp4</t>
+  </si>
+  <si>
+    <t>PHR-SOC-012</t>
+  </si>
+  <si>
+    <t>Are you having fun?</t>
+  </si>
+  <si>
+    <t>អ្នកសប្បាយទេ?</t>
+  </si>
+  <si>
+    <t>Nak sabay te?</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-012.mp4</t>
+  </si>
+  <si>
+    <t>Lets drink beer</t>
+  </si>
+  <si>
+    <t>តោះផឹកស្រាបៀរ</t>
+  </si>
+  <si>
+    <t>Tos phek sra beer</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-013.mp4</t>
+  </si>
+  <si>
+    <t>PHR-SOC-013</t>
+  </si>
+  <si>
+    <t>I like Cambodia</t>
+  </si>
+  <si>
+    <t>ខ្ញុំចូលចិត្តកម្ពុជា</t>
+  </si>
+  <si>
+    <t>Khnhom jol jet Kampuchea</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-014.mp4</t>
+  </si>
+  <si>
+    <t>PHR-SOC-014</t>
+  </si>
+  <si>
+    <t>PHR-SOC-015</t>
+  </si>
+  <si>
+    <t>You make me laugh</t>
+  </si>
+  <si>
+    <t>អ្នកធ្វើឲ្យខ្ញុំសើច</t>
+  </si>
+  <si>
+    <t>Nak tveu oy khnhom sigh</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-SOC-015.mp4</t>
+  </si>
+  <si>
+    <t>PHR-NUM-011</t>
+  </si>
+  <si>
+    <t>One</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eight </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten </t>
+  </si>
+  <si>
+    <t>Twenty</t>
+  </si>
+  <si>
+    <t>M'pei</t>
+  </si>
+  <si>
+    <t>ម្ភៃ</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mickalacki/talktuktuk/main/PHR-NUM-011.mp4</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1176,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1061,6 +1227,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1366,12 +1544,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="4" width="25" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="26.85546875" customWidth="1"/>
     <col min="5" max="5" width="77.85546875" customWidth="1"/>
     <col min="6" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
@@ -1806,7 +1985,7 @@
       <c r="D17" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="20" t="s">
         <v>92</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -1819,73 +1998,73 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H18" s="6" t="s">
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" s="6" t="s">
+      <c r="A19" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>98</v>
@@ -1899,19 +2078,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>98</v>
@@ -1925,19 +2104,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>98</v>
@@ -1950,72 +2129,72 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" s="8" t="s">
+      <c r="A23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" s="8" t="s">
+      <c r="A24" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>125</v>
@@ -2029,19 +2208,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>125</v>
@@ -2055,19 +2234,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>125</v>
@@ -2081,19 +2260,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>276</v>
+        <v>138</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>277</v>
+        <v>139</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>279</v>
+        <v>140</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>141</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>125</v>
@@ -2107,19 +2286,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>293</v>
+        <v>142</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>295</v>
+        <v>143</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>297</v>
+        <v>144</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>125</v>
@@ -2132,715 +2311,1014 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="D40" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="E40" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="F40" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="G40" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="H40" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="B41" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="C41" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="H30" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
+      <c r="D41" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="E41" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="F41" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="B42" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="D42" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
+      <c r="E42" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="F42" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="B43" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="C43" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D43" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E43" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
+      <c r="F43" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B44" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C44" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="D44" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="E44" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="F44" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+      <c r="B45" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C45" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="D45" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="E45" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="F45" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="B46" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C46" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F34" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
+      <c r="D46" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="E46" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="F46" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="B47" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="C47" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="D47" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+      <c r="E47" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="F47" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="B48" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="C48" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D48" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E48" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+      <c r="F48" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B49" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="C49" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="D49" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="E49" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="F49" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="B51" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="C51" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="D51" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="F51" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="G51" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="F38" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
+      <c r="H51" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B52" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C52" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D52" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="F52" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+      <c r="B53" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="C53" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="D53" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="E53" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="E40" s="13" t="s">
+      <c r="F53" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="B54" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="G40" s="12" t="s">
+      <c r="C54" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="H40" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="D54" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="E54" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="F54" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="H54" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="B55" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="D41" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="E41" s="13" t="s">
+      <c r="C55" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="F41" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
+      <c r="D55" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E55" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="F55" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="H55" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="B56" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="E42" s="13" t="s">
+      <c r="C56" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="F42" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
+      <c r="D56" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E56" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="F56" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="H56" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="B57" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="D43" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="E43" s="13" t="s">
+      <c r="C57" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="F43" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
+      <c r="D57" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="E57" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="F57" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="B58" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="D44" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="E44" s="13" t="s">
+      <c r="C58" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="F44" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
+      <c r="D58" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="E58" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="F58" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G58" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="B60" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="D45" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="E45" s="13" t="s">
+      <c r="C60" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="H45" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
+      <c r="D60" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="E60" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="F60" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="E46" s="13" t="s">
+      <c r="G60" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="F46" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="H46" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
+      <c r="H60" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B61" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C61" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="D47" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="E47" s="17" t="s">
+      <c r="D61" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="F47" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="H47" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+      <c r="E61" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="F61" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="G61" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="B62" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="C62" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="D62" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="E62" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="G49" s="14" t="s">
+      <c r="F62" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="H49" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+      <c r="B63" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="C63" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="D63" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="E63" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="F63" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="G63" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H63" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="F50" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="G50" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+      <c r="B64" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="C64" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="D64" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="E64" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="F64" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H64" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="F51" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="G51" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
+      <c r="B65" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="C65" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="D65" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="E65" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="F65" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="G65" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H65" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="F52" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+      <c r="B66" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="C66" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="D66" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="E66" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="F66" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="F53" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="G53" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
+      <c r="B67" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="C67" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="D67" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="E67" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="E54" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="F54" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="G54" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="H54" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="B55" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="E55" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="F55" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="G55" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="H55" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="F56" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="G56" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="H56" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B57">
-        <f ca="1">B2:B57</f>
+      <c r="F67" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H67" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B68">
+        <f ca="1">B2:B68</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E28" r:id="rId1" xr:uid="{9D7F697B-04A3-43D8-834D-1DD935D30A27}"/>
-    <hyperlink ref="E47" r:id="rId2" xr:uid="{AD381954-74B6-4661-84EC-9487E2F47034}"/>
-    <hyperlink ref="E48" r:id="rId3" xr:uid="{7F578AA3-EA40-4432-9E0B-F9D624BADC2E}"/>
-    <hyperlink ref="E29" r:id="rId4" xr:uid="{DAF45DFB-C92C-447D-B376-A4C3C7A10344}"/>
+    <hyperlink ref="E30" r:id="rId1" xr:uid="{9D7F697B-04A3-43D8-834D-1DD935D30A27}"/>
+    <hyperlink ref="E58" r:id="rId2" xr:uid="{AD381954-74B6-4661-84EC-9487E2F47034}"/>
+    <hyperlink ref="E59" r:id="rId3" xr:uid="{7F578AA3-EA40-4432-9E0B-F9D624BADC2E}"/>
+    <hyperlink ref="E31" r:id="rId4" xr:uid="{DAF45DFB-C92C-447D-B376-A4C3C7A10344}"/>
+    <hyperlink ref="E32" r:id="rId5" xr:uid="{B272E3C2-EAF0-4097-90DA-55149A09AB70}"/>
+    <hyperlink ref="E33" r:id="rId6" xr:uid="{3215EC29-56C0-4919-8220-611019DCA0A7}"/>
+    <hyperlink ref="E34" r:id="rId7" xr:uid="{F6629DBE-D3F8-4889-A998-CA9E77F2135E}"/>
+    <hyperlink ref="E17" r:id="rId8" xr:uid="{B0990B0F-7D59-4643-B8C8-1267F6FE3878}"/>
+    <hyperlink ref="E18" r:id="rId9" xr:uid="{3A4E4CB0-5230-4DEA-9839-CD5ADF5591B1}"/>
+    <hyperlink ref="E19" r:id="rId10" xr:uid="{F2823B24-50AD-421B-AD2A-FD90D2F04B3B}"/>
+    <hyperlink ref="E35" r:id="rId11" xr:uid="{79078E22-42F5-41FC-8365-C972AA27699A}"/>
+    <hyperlink ref="E36" r:id="rId12" xr:uid="{87C5F770-5CDE-4625-BD37-CB1F59A1FB46}"/>
+    <hyperlink ref="E37" r:id="rId13" xr:uid="{F0AE244D-C007-4885-AC35-F0758CE07801}"/>
+    <hyperlink ref="E38" r:id="rId14" xr:uid="{3B666059-6E4C-43D6-8ED0-DBB151DA8D12}"/>
+    <hyperlink ref="E39" r:id="rId15" xr:uid="{73458B9E-C659-4C47-AD5A-1F3BF192E564}"/>
+    <hyperlink ref="E49" r:id="rId16" xr:uid="{16DAF835-D4BD-4AD9-9AD4-AD98BE955937}"/>
+    <hyperlink ref="E50" r:id="rId17" xr:uid="{ACD2B0C5-E06D-4267-AB4C-FCFDEE27872D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TalkTukTuk_Phrases.xlsx
+++ b/TalkTukTuk_Phrases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TOSHIBA\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60843701-2E70-421C-BE41-0BE17BF67CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74A3C2A-DAA2-4417-B5E0-1E76B247C6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="420" yWindow="510" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="350">
   <si>
     <t>PhraseID</t>
   </si>
@@ -1035,6 +1035,42 @@
   </si>
   <si>
     <t>Trey</t>
+  </si>
+  <si>
+    <t>PHR-FOO-016</t>
+  </si>
+  <si>
+    <t>Prawns</t>
+  </si>
+  <si>
+    <t>បង្គា</t>
+  </si>
+  <si>
+    <t>Bongkea</t>
+  </si>
+  <si>
+    <t>PHR-FOO-017</t>
+  </si>
+  <si>
+    <t>French fries</t>
+  </si>
+  <si>
+    <t>ដំឡូងបារាំងបំពង</t>
+  </si>
+  <si>
+    <t>Domlong Barang Bompong</t>
+  </si>
+  <si>
+    <t>PHR-FOO-018</t>
+  </si>
+  <si>
+    <t>Bread</t>
+  </si>
+  <si>
+    <t>នំប៉័ង</t>
+  </si>
+  <si>
+    <t>Nom Pang</t>
   </si>
 </sst>
 </file>
@@ -1453,7 +1489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1994,86 +2030,86 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="A24" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="A25" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="A26" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>80</v>
@@ -2087,16 +2123,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>80</v>
@@ -2110,16 +2146,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>286</v>
+        <v>86</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>287</v>
+        <v>87</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>288</v>
+        <v>88</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>80</v>
@@ -2133,16 +2169,16 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>290</v>
+        <v>90</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>291</v>
+        <v>91</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>292</v>
+        <v>92</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>293</v>
+        <v>93</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>80</v>
@@ -2156,16 +2192,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>294</v>
+        <v>94</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>295</v>
+        <v>95</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>296</v>
+        <v>96</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>297</v>
+        <v>97</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>80</v>
@@ -2179,16 +2215,16 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>80</v>
@@ -2201,86 +2237,86 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G33" s="5" t="s">
+      <c r="A33" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G34" s="5" t="s">
+      <c r="A34" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G35" s="5" t="s">
+      <c r="A35" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>102</v>
@@ -2294,16 +2330,16 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>231</v>
+        <v>105</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>102</v>
@@ -2317,16 +2353,16 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>211</v>
+        <v>108</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>213</v>
+        <v>110</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>214</v>
+        <v>111</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>102</v>
@@ -2340,16 +2376,16 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>227</v>
+        <v>112</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>228</v>
+        <v>113</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>229</v>
+        <v>114</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>230</v>
+        <v>115</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>102</v>
@@ -2363,16 +2399,16 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>232</v>
+        <v>116</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>234</v>
+        <v>117</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>235</v>
+        <v>118</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>102</v>
@@ -2386,16 +2422,16 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>243</v>
+        <v>212</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>102</v>
@@ -2409,16 +2445,16 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>241</v>
+        <v>228</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>102</v>
@@ -2432,16 +2468,16 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>254</v>
+        <v>233</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>102</v>
@@ -2455,16 +2491,16 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>102</v>
@@ -2478,16 +2514,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>102</v>
@@ -2501,16 +2537,16 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>102</v>
@@ -2524,16 +2560,16 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>102</v>
@@ -2546,86 +2582,86 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="A48" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G48" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G49" s="6" t="s">
+      <c r="A49" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G49" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="A50" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>122</v>
@@ -2639,16 +2675,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>122</v>
@@ -2662,16 +2698,16 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>122</v>
@@ -2685,16 +2721,16 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>122</v>
@@ -2708,16 +2744,16 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>122</v>
@@ -2731,16 +2767,16 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>122</v>
@@ -2754,16 +2790,16 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>122</v>
@@ -2777,16 +2813,16 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>285</v>
+        <v>143</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>284</v>
+        <v>144</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>122</v>
@@ -2799,86 +2835,86 @@
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G59" s="7" t="s">
+      <c r="A59" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G59" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G60" s="7" t="s">
+      <c r="A60" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G61" s="7" t="s">
+      <c r="A61" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G61" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>154</v>
@@ -2892,16 +2928,16 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>154</v>
@@ -2915,16 +2951,16 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>154</v>
@@ -2938,16 +2974,16 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>154</v>
@@ -2961,16 +2997,16 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>154</v>
@@ -2984,16 +3020,16 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>154</v>
@@ -3007,16 +3043,16 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>306</v>
+        <v>171</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>307</v>
+        <v>172</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>308</v>
+        <v>173</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>309</v>
+        <v>225</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>154</v>
@@ -3030,16 +3066,16 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>310</v>
+        <v>174</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>311</v>
+        <v>175</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>312</v>
+        <v>176</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>313</v>
+        <v>226</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>154</v>
@@ -3053,16 +3089,16 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>314</v>
+        <v>215</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>316</v>
+        <v>216</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>217</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>317</v>
+        <v>218</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>154</v>
@@ -3076,16 +3112,16 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>320</v>
+        <v>307</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>308</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>154</v>
@@ -3098,86 +3134,86 @@
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G72" s="8" t="s">
+      <c r="A72" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G72" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G73" s="8" t="s">
+      <c r="A73" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G73" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G74" s="8" t="s">
+      <c r="A74" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G74" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>181</v>
@@ -3191,16 +3227,16 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>181</v>
@@ -3214,16 +3250,16 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>181</v>
@@ -3237,16 +3273,16 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>181</v>
@@ -3260,16 +3296,16 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>181</v>
@@ -3283,16 +3319,16 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="B80" t="s">
-        <v>304</v>
+        <v>199</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>302</v>
+        <v>201</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>303</v>
+        <v>202</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>181</v>
@@ -3301,6 +3337,75 @@
         <v>182</v>
       </c>
       <c r="G80" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B83" t="s">
+        <v>304</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G83" s="8" t="s">
         <v>13</v>
       </c>
     </row>
